--- a/Client/Configs/GameConfig/Datas/buff.xlsx
+++ b/Client/Configs/GameConfig/Datas/buff.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,43 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <color rgb="007F6000"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,20 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,81 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Buff预留表：后续做减速、眩晕、光环、持续伤害时使用。当前原型可以先不改。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Buff ID。0固定表示没有Buff。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Buff Key。程序识别用。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Buff显示名。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Buff类型。None/Dot/Hot/StatModifier/Control/Aura 等。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>持续时间，单位秒。0表示无持续时间。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>最大叠层。0或1表示不可叠加；大于1表示可叠层。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>跳频，单位秒。持续伤害/治疗每隔多久结算一次。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>影响的属性。None/Attack/MoveSpeed/CastSpeed 等。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>修改方式。None/Add/Percent/Mul 等。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>修改值。比如移速-30%可填 -0.3。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>控制标记。None/Stun/Silence/Root 等，可用逗号组合。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>光环半径，单位米。0表示不是光环。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,345 +413,563 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>buffKey</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>buffType</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>maxStack</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tickInterval</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>statType</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>modifierType</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>modifierValue</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>controlFlags</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>auraRadius</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>auraBuffId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Buff ID。0固定表示没有Buff。</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Buff Key。程序识别用。</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Buff显示名。</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Buff类型。None/Dot/Hot/StatModifier/Control/Aura 等。</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>持续时间，单位秒。0表示无持续时间。</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>最大叠层。0或1表示不可叠加；大于1表示可叠层。</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>跳频，单位秒。持续伤害/治疗每隔多久结算一次。</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>影响的属性。None/Attack/MoveSpeed/CastSpeed 等。</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>修改方式。None/Add/Percent/Mul 等。</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>修改值。比如移速-30%可填 -0.3。</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>控制标记。None/Stun/Silence/Root 等，可用逗号组合。</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>光环半径，单位米。0表示不是光环。</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Buff id.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Buff key.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Display name.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Buff type.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duration.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Max stack.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tick interval.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Stat type.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Modifier type.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Modifier value.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Control flags.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Aura radius.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Aura child buff id.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>无Buff</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>500101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>frost_slow</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Frost Slow</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>500201</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fire_burn</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DamageOverTime</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>500400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>devotion_aura</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Devotion Aura</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>500401</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>500401</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>devotion_aura_armor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Devotion Armor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Client/Configs/GameConfig/Datas/buff.xlsx
+++ b/Client/Configs/GameConfig/Datas/buff.xlsx
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-0.25</v>
+        <v>-0.6</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/Client/Configs/GameConfig/Datas/buff.xlsx
+++ b/Client/Configs/GameConfig/Datas/buff.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,69 +865,69 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>500400</v>
+        <v>500301</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>devotion_aura</t>
+          <t>charge_stun</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Devotion Aura</t>
+          <t>Charge Stun</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>StatModifier</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>999</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AttackSpeed</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>500401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>500401</v>
+        <v>500302</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>devotion_aura_armor</t>
+          <t>thunder_clap_slow</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Devotion Armor</t>
+          <t>Thunder Clap Slow</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -946,26 +946,132 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>500400</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>devotion_aura</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Devotion Aura</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>500401</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>500401</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>devotion_armor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Devotion Armor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Armor</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
